--- a/data/Item.xlsx
+++ b/data/Item.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2133,6 +2133,318 @@
         <v>1</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B54" t="n">
+        <v>999</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>强化石</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>强化装备时消耗的材料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B55" t="n">
+        <v>999</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>攻击宝石·一级</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>可镶嵌在装备的攻击孔或通用孔,提升伤害。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2102</v>
+      </c>
+      <c r="B56" t="n">
+        <v>999</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>攻击宝石·二级</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>可镶嵌在装备的攻击孔或通用孔,提升伤害。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B57" t="n">
+        <v>999</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>攻击宝石·三级</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>可镶嵌在装备的攻击孔或通用孔,提升伤害。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2201</v>
+      </c>
+      <c r="B58" t="n">
+        <v>999</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>防御宝石·一级</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>可镶嵌在装备的防御孔或通用孔,提升防御。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2202</v>
+      </c>
+      <c r="B59" t="n">
+        <v>999</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>防御宝石·二级</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>可镶嵌在装备的防御孔或通用孔,提升防御。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2203</v>
+      </c>
+      <c r="B60" t="n">
+        <v>999</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>防御宝石·三级</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>可镶嵌在装备的防御孔或通用孔,提升防御。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2301</v>
+      </c>
+      <c r="B61" t="n">
+        <v>999</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>气血宝石·一级</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>可镶嵌在装备的气血孔或通用孔,提升气血。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2302</v>
+      </c>
+      <c r="B62" t="n">
+        <v>999</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>气血宝石·二级</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>可镶嵌在装备的气血孔或通用孔,提升气血。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2303</v>
+      </c>
+      <c r="B63" t="n">
+        <v>999</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>气血宝石·三级</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>可镶嵌在装备的气血孔或通用孔,提升气血。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2401</v>
+      </c>
+      <c r="B64" t="n">
+        <v>999</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>迅捷宝石·一级</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>可镶嵌在装备的迅捷孔或通用孔,提升速度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2402</v>
+      </c>
+      <c r="B65" t="n">
+        <v>999</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>迅捷宝石·二级</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>可镶嵌在装备的迅捷孔或通用孔,提升速度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2403</v>
+      </c>
+      <c r="B66" t="n">
+        <v>999</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>迅捷宝石·三级</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>可镶嵌在装备的迅捷孔或通用孔,提升速度。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
